--- a/public/assets/BOs/Kronos.xlsx
+++ b/public/assets/BOs/Kronos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79672E4C-66FE-4263-883D-51DCDC55327B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D297994-8845-4A8A-A204-F0A6C81035B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil2" sheetId="3" r:id="rId1"/>
@@ -748,9 +748,6 @@
     <t>Krush 6 vill - Defiance</t>
   </si>
   <si>
-    <t>Oranos/Kronos - 6 Citizen Rush BO - By Chonikler IV</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1004,6 +1001,9 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=GZhVM3WpLeA</t>
+  </si>
+  <si>
+    <t>Oranos/Kronos - 6 Citizen Rush BO - By ChoniclerIV</t>
   </si>
 </sst>
 </file>
@@ -1014,11 +1014,18 @@
     <numFmt numFmtId="164" formatCode="[$-410]General"/>
     <numFmt numFmtId="165" formatCode="[$€-410]&quot; &quot;#,##0.00;[Red]&quot;-&quot;[$€-410]&quot; &quot;#,##0.00"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1253,91 +1260,91 @@
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Excel Built-in Hyperlink" xfId="3" xr:uid="{AF420925-7D11-4B4B-B056-D95B36C2C522}"/>
@@ -1657,12 +1664,12 @@
       <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" ht="15.6">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
     </row>
     <row r="12" spans="1:4" ht="13.8">
       <c r="A12" s="4" t="s">
@@ -1729,137 +1736,137 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.6">
+      <c r="A2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="1:4" ht="13.8">
+      <c r="A3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="13.8">
+      <c r="A4" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.6">
-      <c r="A2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" spans="1:4" ht="13.8">
-      <c r="A3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-    </row>
-    <row r="4" spans="1:4" ht="13.8">
-      <c r="A4" s="27" t="s">
+      <c r="B4" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="26"/>
-      <c r="D4" s="28" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="13.8">
+      <c r="A5" s="19" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.8">
-      <c r="A5" s="27" t="s">
+      <c r="B5" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="13.8">
+      <c r="A6" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D5" s="26"/>
-    </row>
-    <row r="6" spans="1:4" ht="13.8">
-      <c r="A6" s="27" t="s">
+      <c r="B6" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4" ht="13.8">
+      <c r="A7" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="26"/>
-    </row>
-    <row r="7" spans="1:4" ht="13.8">
-      <c r="A7" s="27" t="s">
+      <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="C7" s="20"/>
+      <c r="D7" s="18"/>
+    </row>
+    <row r="8" spans="1:4" ht="13.8">
+      <c r="A8" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="26"/>
-    </row>
-    <row r="8" spans="1:4" ht="13.8">
-      <c r="A8" s="27" t="s">
+      <c r="B8" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="C8" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4" ht="13.8">
+      <c r="A9" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="26"/>
-    </row>
-    <row r="9" spans="1:4" ht="13.8">
-      <c r="A9" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" s="26"/>
+      <c r="B9" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="18"/>
     </row>
     <row r="10" spans="1:4" ht="15.6">
       <c r="A10" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+    </row>
+    <row r="11" spans="1:4" ht="13.8">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="1:4" ht="13.8">
+      <c r="A12" s="18"/>
+      <c r="B12" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-    </row>
-    <row r="11" spans="1:4" ht="13.8">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-    </row>
-    <row r="12" spans="1:4" ht="13.8">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28" t="s">
+      <c r="D12" s="18"/>
+    </row>
+    <row r="13" spans="1:4" ht="13.8">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="26"/>
-    </row>
-    <row r="13" spans="1:4" ht="13.8">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="32" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="33"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
     </row>
     <row r="16" spans="1:4" ht="15">
-      <c r="A16" s="34"/>
+      <c r="A16" s="24"/>
     </row>
     <row r="17" spans="1:2" ht="15">
-      <c r="A17" s="34"/>
+      <c r="A17" s="24"/>
     </row>
     <row r="18" spans="1:2" ht="15">
-      <c r="A18" s="34"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="8"/>
     </row>
     <row r="19" spans="1:2">
@@ -1891,18 +1898,18 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="13.8">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="13.8">
       <c r="A3" s="1" t="s">
@@ -1993,12 +2000,12 @@
       <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" ht="15.6">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
     </row>
     <row r="13" spans="1:4" ht="13.8">
       <c r="A13" s="4" t="s">
@@ -2142,20 +2149,20 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2"/>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" ht="15.6">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
     </row>
     <row r="3" spans="1:4" ht="15">
       <c r="A3" s="10" t="s">
@@ -2216,12 +2223,12 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.6">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
     </row>
     <row r="9" spans="1:4" ht="15">
       <c r="A9" s="10" t="s">
@@ -2246,12 +2253,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.6">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
     </row>
     <row r="12" spans="1:4" ht="19.8">
       <c r="A12" s="10" t="s">
